--- a/tools/importer/reports/import-hero-feature-landing.report.xlsx
+++ b/tools/importer/reports/import-hero-feature-landing.report.xlsx
@@ -67,7 +67,7 @@
     <t>html-sitemap</t>
   </si>
   <si>
-    <t>2026-09-21T14:24:19.675Z</t>
+    <t>2026-09-22T10:47:15.220Z</t>
   </si>
   <si>
     <t>HTML Sitemap</t>
@@ -88,7 +88,7 @@
     <t>hero-feature-landing</t>
   </si>
   <si>
-    <t>2026-09-21T14:45:16.162Z</t>
+    <t>2026-09-22T10:49:46.943Z</t>
   </si>
   <si>
     <t>Home - Pet Care Network | Destination Pet</t>
@@ -124,7 +124,7 @@
     <t>live-webinar</t>
   </si>
   <si>
-    <t>2026-09-21T14:22:31.137Z</t>
+    <t>2026-09-22T10:50:35.910Z</t>
   </si>
   <si>
     <t>A Series of Webinars | Destination Pet</t>
@@ -142,7 +142,7 @@
     <t>our-locations</t>
   </si>
   <si>
-    <t>2026-09-21T14:23:06.103Z</t>
+    <t>2026-09-22T10:51:10.388Z</t>
   </si>
   <si>
     <t>Our Locations | Destination Pet</t>
@@ -178,7 +178,7 @@
     <t>sell-your-business</t>
   </si>
   <si>
-    <t>2026-09-21T14:23:15.187Z</t>
+    <t>2026-09-22T10:51:19.565Z</t>
   </si>
   <si>
     <t>Sell Your Veterinary | Destination Pet</t>
@@ -211,7 +211,7 @@
     <t>about-us/about</t>
   </si>
   <si>
-    <t>2026-09-21T14:21:53.532Z</t>
+    <t>2026-09-22T10:49:53.900Z</t>
   </si>
   <si>
     <t>About Us | Destination Pet, LLC</t>
@@ -262,7 +262,7 @@
     <t>about-us/get-in-touch</t>
   </si>
   <si>
-    <t>2026-09-21T14:22:03.236Z</t>
+    <t>2026-09-22T10:50:03.179Z</t>
   </si>
   <si>
     <t>Contact Us | Destination Pet, LLC</t>
@@ -310,7 +310,7 @@
     <t>join-our-pack/find-a-veterinary-externship</t>
   </si>
   <si>
-    <t>2026-09-21T14:22:21.694Z</t>
+    <t>2026-09-22T10:50:24.456Z</t>
   </si>
   <si>
     <t>Find a Veterinary Externship - Destination Pet</t>
@@ -325,7 +325,7 @@
     <t>join-our-pack/life-at-dp</t>
   </si>
   <si>
-    <t>2026-09-21T14:22:26.342Z</t>
+    <t>2026-09-22T10:50:29.741Z</t>
   </si>
   <si>
     <t>life at Destination Pet | Destination Pet</t>
@@ -340,7 +340,7 @@
     <t>live-webinar/webinar-redirect</t>
   </si>
   <si>
-    <t>2026-09-21T14:22:37.079Z</t>
+    <t>2026-09-22T10:50:43.081Z</t>
   </si>
   <si>
     <t>Webinar Redirect - Destination Pet</t>
@@ -355,7 +355,7 @@
     <t>live-webinar/webinar-registration</t>
   </si>
   <si>
-    <t>2026-09-21T14:22:45.811Z</t>
+    <t>2026-09-22T10:50:51.975Z</t>
   </si>
   <si>
     <t>Webinar Registration - Destination Pet</t>
@@ -370,7 +370,7 @@
     <t>live-webinar/webinar-viewing-previous</t>
   </si>
   <si>
-    <t>2026-09-21T14:22:54.107Z</t>
+    <t>2026-09-22T10:50:59.242Z</t>
   </si>
   <si>
     <t>Webinar Viewing Previous - Destination Pet</t>
@@ -385,7 +385,7 @@
     <t>live-webinar/webinars-for-pet</t>
   </si>
   <si>
-    <t>2026-09-21T14:22:59.048Z</t>
+    <t>2026-09-22T10:51:04.285Z</t>
   </si>
   <si>
     <t>Webinars for Pet - Destination Pet</t>
@@ -421,7 +421,7 @@
     <t>sell-your-business/sell-your-pet-resort</t>
   </si>
   <si>
-    <t>2026-09-21T14:23:20.873Z</t>
+    <t>2026-09-22T10:51:25.442Z</t>
   </si>
   <si>
     <t>Sell Your Pet Resort - Destination Pet</t>
@@ -436,7 +436,7 @@
     <t>sell-your-business/sell-your-veterinary-practice</t>
   </si>
   <si>
-    <t>2026-09-21T14:23:26.573Z</t>
+    <t>2026-09-22T10:51:32.074Z</t>
   </si>
   <si>
     <t>Sell your veterinary practice | Destination Pet</t>
@@ -454,7 +454,7 @@
     <t>about-us/meet-the-team/business-development-leaders</t>
   </si>
   <si>
-    <t>2026-09-21T14:22:07.743Z</t>
+    <t>2026-09-22T10:50:09.519Z</t>
   </si>
   <si>
     <t>Business Development Leaders | Destination Pet</t>
@@ -472,7 +472,7 @@
     <t>about-us/meet-the-team/leadership</t>
   </si>
   <si>
-    <t>2026-09-21T14:22:14.540Z</t>
+    <t>2026-09-22T10:50:16.089Z</t>
   </si>
   <si>
     <t>Leadership - Meet the team | Destination Pet</t>
